--- a/sablona/data/vtupni_obsah_zkouska.xlsx
+++ b/sablona/data/vtupni_obsah_zkouska.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rycht\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rycht\Documents\homologizer_aconitum\sablona\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA2B55B-07AD-41A1-B47D-2D14B6AE5F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FA4236-42E4-4981-8088-1776BB8967BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -82,9 +82,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -111,15 +109,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -428,16 +423,16 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>3</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="1"/>
@@ -446,16 +441,16 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
     </row>
@@ -463,16 +458,16 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
         <v>4</v>
       </c>
       <c r="F4" s="1"/>
@@ -481,16 +476,16 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
         <v>4</v>
       </c>
       <c r="F5" s="1"/>
@@ -499,54 +494,54 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <v>4</v>
       </c>
     </row>
